--- a/templates/invoice/invoice template.xlsx
+++ b/templates/invoice/invoice template.xlsx
@@ -1,130 +1,224 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liyon\Desktop\Printer-Service-System\templates\invoice\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF1DE4C-AD0B-4FC6-AB8C-F5E90A00134E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$G$20</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
-  <si>
-    <t xml:space="preserve">{{company_name}}
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+  <si>
+    <t>No.</t>
+  </si>
+  <si>
+    <t>ITEM NO</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Qty</t>
+  </si>
+  <si>
+    <t>Unit Price (KES)</t>
+  </si>
+  <si>
+    <t>Amount (KES)</t>
+  </si>
+  <si>
+    <t>Subtotal (KES)</t>
+  </si>
+  <si>
+    <t>VAT</t>
+  </si>
+  <si>
+    <t>Total (KES)</t>
+  </si>
+  <si>
+    <t>INVOICE</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ENFB WAJIKU TRADING LIMITED
 P.O.BOX 5117 - 00100, Nairobi, Kenya
 PIN: P052072205J
 </t>
-  </si>
-  <si>
-    <t>INVOICE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CUSTOMER : {{customer_name}}
-PIN : {{pin_no}}</t>
-  </si>
-  <si>
-    <t>Date: {{date}}</t>
-  </si>
-  <si>
-    <t>INVOICE No.: {{invoice_no}}</t>
-  </si>
-  <si>
-    <t>No.</t>
-  </si>
-  <si>
-    <t>ITEM NO</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Description</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Qty</t>
-  </si>
-  <si>
-    <t>Unit Price (KES)</t>
-  </si>
-  <si>
-    <t>Amount (KES)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RECEIVED BY: {{created_by}}
-Amount in words: {{total_in_words}}</t>
-  </si>
-  <si>
-    <t>Subtotal (KES)</t>
-  </si>
-  <si>
-    <t>{{subtotal}}</t>
-  </si>
-  <si>
-    <t>VAT</t>
-  </si>
-  <si>
-    <t>{{vat}}</t>
-  </si>
-  <si>
-    <t>Total (KES)</t>
-  </si>
-  <si>
-    <t>{{grand_total}}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Customer:
+{{CUSTOMER_NAME}}
+PIN: {{CUSTOMER_PIN}}
+</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Date:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> {{INVOICE_DATE}}</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>INVOICE No.:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> {{INVOICE_NO}}</t>
+    </r>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{ITEM_NO}}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{ITEM_NAME}}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{DESCRIPTION}}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{UNIT}}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{QTY}}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{UNIT_PRICE}}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{AMOUNT}}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{SUBTOTAL}}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{VAT_AMOUNT}}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{TOTAL_AMOUNT}}</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * -#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <family val="2"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <charset val="134"/>
-      <color theme="1"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="等线"/>
     </font>
     <font>
       <b/>
+      <sz val="14"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
-      <sz val="18"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <family val="1"/>
-      <sz val="18"/>
-      <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
+      <sz val="18"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
-      <sz val="14"/>
-      <name val="Times New Roman"/>
     </font>
     <font>
+      <sz val="18"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
       <family val="1"/>
-      <sz val="14"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -135,7 +229,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -144,35 +238,55 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right/>
-      <top style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin"/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin"/>
-      <top style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right/>
       <top/>
       <bottom/>
@@ -180,59 +294,126 @@
     </border>
     <border>
       <left/>
-      <right style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right/>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -241,89 +422,79 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -348,17 +519,17 @@
       <xdr:rowOff>76970</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1039092</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>694</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>1212597</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 1">
+        <xdr:cNvPr id="2" name="图片 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B41FD43-AC1E-DF49-86AE-AFC18D6842DB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -367,15 +538,15 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
+          <a:off x="8210101" y="76970"/>
+          <a:ext cx="1475254" cy="1135627"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -644,276 +815,285 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultRowHeight="14.15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" defaultColWidth="9" customHeight="1"/>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.640625" customWidth="1"/>
     <col min="2" max="2" width="13.5" customWidth="1"/>
     <col min="3" max="3" width="22.640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="22.640625" customWidth="1"/>
     <col min="5" max="5" width="28.35546875" customWidth="1"/>
-    <col min="6" max="6" width="20.35546875" customWidth="1"/>
-    <col min="7" max="7" width="17.35546875" customWidth="1"/>
+    <col min="6" max="6" width="16.35546875" customWidth="1"/>
+    <col min="7" max="7" width="18.640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="99.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" ht="99.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+    </row>
+    <row r="2" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="15"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+    </row>
+    <row r="3" spans="1:7" ht="50.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="31"/>
+      <c r="B3" s="32"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="26"/>
+      <c r="F3" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="18"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="34"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="18"/>
+    </row>
+    <row r="5" spans="1:7" ht="113.05" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="37"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+    </row>
+    <row r="6" spans="1:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-    </row>
-    <row r="2" ht="29.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-    </row>
-    <row r="3" ht="50.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="6"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="6" t="s">
+      <c r="C6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="10" t="s">
+      <c r="E6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="11"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="17" t="s">
+      <c r="F6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="11"/>
-    </row>
-    <row r="5" ht="113.05" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
-    </row>
-    <row r="6" ht="40.3" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="G6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="24" t="s">
+    </row>
+    <row r="7" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="4">
+        <v>2</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+    </row>
+    <row r="9" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="4">
+        <v>3</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+    </row>
+    <row r="10" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="4">
+        <v>4</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="6"/>
+    </row>
+    <row r="11" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="4">
+        <v>5</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+    </row>
+    <row r="12" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="4">
         <v>6</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="B12" s="4"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+    </row>
+    <row r="13" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="4">
         <v>7</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="B13" s="4"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="7"/>
+    </row>
+    <row r="14" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="4">
         <v>8</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="B14" s="4"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="7"/>
+    </row>
+    <row r="15" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="4">
         <v>9</v>
       </c>
-      <c r="F6" s="23" t="s">
+      <c r="B15" s="4"/>
+      <c r="C15" s="5"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="7"/>
+    </row>
+    <row r="16" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="4">
         <v>10</v>
       </c>
-      <c r="G6" s="23" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" ht="80.05" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="25">
-        <v>1</v>
-      </c>
-      <c r="B7" s="25"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27">
-        <f>E7*F7</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="80.05" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="25">
-        <v>2</v>
-      </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27">
-        <f t="shared" ref="G8:G14" si="0">E8*F8</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="80.05" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="25">
-        <v>3</v>
-      </c>
-      <c r="B9" s="25"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="80.05" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="25">
-        <v>4</v>
-      </c>
-      <c r="B10" s="25"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="80.05" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="25">
-        <v>5</v>
-      </c>
-      <c r="B11" s="25"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="80.05" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="25">
+      <c r="B16" s="4"/>
+      <c r="C16" s="5"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="23"/>
+      <c r="B17" s="23"/>
+      <c r="C17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="25"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="80.05" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="25">
+      <c r="G17" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="24"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="25"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="80.05" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="25">
+      <c r="G18" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="24"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="25"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="23.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="10"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="29" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" ht="21" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="10"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="10"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" s="29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="G17" s="31" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" ht="41.25" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="33"/>
+      <c r="G19" s="21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="41.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="24"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="A17:E20"/>
+    <mergeCell ref="F4:G5"/>
+    <mergeCell ref="D3:E5"/>
     <mergeCell ref="A3:C5"/>
-    <mergeCell ref="D3:E5"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="F4:G5"/>
-    <mergeCell ref="A15:E18"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="G17:G18"/>
   </mergeCells>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="64" fitToWidth="1" fitToHeight="0" firstPageNumber="1" useFirstPageNumber="1" copies="2"/>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="67" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>